--- a/src/test/resources/teammapping.xlsx
+++ b/src/test/resources/teammapping.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="searchrecruiter" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Yes</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t xml:space="preserve">Lokesh </t>
-  </si>
-  <si>
-    <t>Apollo</t>
   </si>
   <si>
     <t xml:space="preserve">Input </t>
@@ -486,18 +483,18 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
+      <c r="A2">
+        <v>866544</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -517,18 +514,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -549,24 +546,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
